--- a/Analysis/raw data/Survey 2 clean_near complete_16.6.26.xlsx
+++ b/Analysis/raw data/Survey 2 clean_near complete_16.6.26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ranidavis/Desktop/Bats &amp; agriculture/Beneficial Bats - collaborative paper/IBRC paper analysis/IBRC beneficial bats survey response analysis/Analysis/raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0E8B6B-88F0-1F41-BD3B-43C342634B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A845E0-336A-2644-9DA7-64A34D8EEBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-2100" windowWidth="28640" windowHeight="19400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="6420" windowWidth="28640" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Survey 2_near complete_16.6.26" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="459">
   <si>
     <t>Status</t>
   </si>
@@ -1226,12 +1226,6 @@
   </si>
   <si>
     <t>R34</t>
-  </si>
-  <si>
-    <t>Multi-country: Australia &amp;New Zealand</t>
-  </si>
-  <si>
-    <t>Australia &amp; New Zealand</t>
   </si>
   <si>
     <t>R35</t>
@@ -2535,7 +2529,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>271</v>
@@ -2559,7 +2553,7 @@
         <v>276</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>16</v>
@@ -2603,7 +2597,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>277</v>
@@ -2627,7 +2621,7 @@
         <v>281</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>28</v>
@@ -2659,7 +2653,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>282</v>
@@ -2683,7 +2677,7 @@
         <v>286</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>34</v>
@@ -2718,7 +2712,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>287</v>
@@ -2742,7 +2736,7 @@
         <v>292</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>39</v>
@@ -2789,7 +2783,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>293</v>
@@ -2813,7 +2807,7 @@
         <v>297</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>47</v>
@@ -2851,7 +2845,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>298</v>
@@ -2875,7 +2869,7 @@
         <v>281</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>52</v>
@@ -2919,7 +2913,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>303</v>
@@ -2943,7 +2937,7 @@
         <v>306</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>58</v>
@@ -2981,7 +2975,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>303</v>
@@ -3005,7 +2999,7 @@
         <v>306</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>63</v>
@@ -3037,7 +3031,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>309</v>
@@ -3061,7 +3055,7 @@
         <v>281</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>65</v>
@@ -3093,7 +3087,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>309</v>
@@ -3117,7 +3111,7 @@
         <v>281</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>67</v>
@@ -3161,7 +3155,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>309</v>
@@ -3185,7 +3179,7 @@
         <v>281</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>75</v>
@@ -3226,7 +3220,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>309</v>
@@ -3250,7 +3244,7 @@
         <v>297</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>80</v>
@@ -3294,7 +3288,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>309</v>
@@ -3318,7 +3312,7 @@
         <v>286</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>85</v>
@@ -3359,7 +3353,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>309</v>
@@ -3383,7 +3377,7 @@
         <v>286</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>85</v>
@@ -3415,7 +3409,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>309</v>
@@ -3439,7 +3433,7 @@
         <v>276</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>91</v>
@@ -3480,7 +3474,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>309</v>
@@ -3504,7 +3498,7 @@
         <v>276</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K17" s="9" t="s">
         <v>95</v>
@@ -3545,7 +3539,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>309</v>
@@ -3569,7 +3563,7 @@
         <v>276</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K18" s="9" t="s">
         <v>97</v>
@@ -3613,7 +3607,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>309</v>
@@ -3637,7 +3631,7 @@
         <v>276</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>97</v>
@@ -3684,7 +3678,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>309</v>
@@ -3708,7 +3702,7 @@
         <v>286</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>85</v>
@@ -3740,7 +3734,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>324</v>
@@ -3764,7 +3758,7 @@
         <v>276</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>103</v>
@@ -3802,7 +3796,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>324</v>
@@ -3826,7 +3820,7 @@
         <v>292</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>108</v>
@@ -3864,7 +3858,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>328</v>
@@ -3888,7 +3882,7 @@
         <v>331</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>112</v>
@@ -3917,7 +3911,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>332</v>
@@ -3941,7 +3935,7 @@
         <v>292</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>113</v>
@@ -3976,7 +3970,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>336</v>
@@ -4000,7 +3994,7 @@
         <v>281</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="L25" s="9" t="s">
         <v>48</v>
@@ -4032,7 +4026,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>339</v>
@@ -4056,7 +4050,7 @@
         <v>331</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>120</v>
@@ -4094,7 +4088,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>343</v>
@@ -4118,7 +4112,7 @@
         <v>306</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>124</v>
@@ -4156,7 +4150,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>347</v>
@@ -4180,7 +4174,7 @@
         <v>292</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>128</v>
@@ -4227,7 +4221,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>351</v>
@@ -4251,7 +4245,7 @@
         <v>292</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>135</v>
@@ -4280,7 +4274,7 @@
         <v>15</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>351</v>
@@ -4304,7 +4298,7 @@
         <v>292</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>136</v>
@@ -4336,7 +4330,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>351</v>
@@ -4360,7 +4354,7 @@
         <v>281</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>75</v>
@@ -4389,7 +4383,7 @@
         <v>15</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>355</v>
@@ -4413,7 +4407,7 @@
         <v>297</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>138</v>
@@ -4454,7 +4448,7 @@
         <v>15</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>355</v>
@@ -4478,7 +4472,7 @@
         <v>281</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>143</v>
@@ -4516,7 +4510,7 @@
         <v>15</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>359</v>
@@ -4540,7 +4534,7 @@
         <v>297</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>147</v>
@@ -4584,7 +4578,7 @@
         <v>15</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>359</v>
@@ -4608,7 +4602,7 @@
         <v>281</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>153</v>
@@ -4655,7 +4649,7 @@
         <v>15</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>362</v>
@@ -4679,7 +4673,7 @@
         <v>286</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K36" s="9" t="s">
         <v>85</v>
@@ -4720,7 +4714,7 @@
         <v>15</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>362</v>
@@ -4744,7 +4738,7 @@
         <v>367</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>164</v>
@@ -4776,7 +4770,7 @@
         <v>15</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>368</v>
@@ -4800,7 +4794,7 @@
         <v>281</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K38" s="9" t="s">
         <v>166</v>
@@ -4832,7 +4826,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>372</v>
@@ -4856,7 +4850,7 @@
         <v>292</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>168</v>
@@ -4897,7 +4891,7 @@
         <v>15</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>374</v>
@@ -4921,7 +4915,7 @@
         <v>292</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K40" s="9" t="s">
         <v>173</v>
@@ -4959,7 +4953,7 @@
         <v>15</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>376</v>
@@ -4983,7 +4977,7 @@
         <v>286</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>178</v>
@@ -5030,7 +5024,7 @@
         <v>15</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>378</v>
@@ -5054,7 +5048,7 @@
         <v>306</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="K42" s="9" t="s">
         <v>185</v>
@@ -5086,7 +5080,7 @@
         <v>15</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>381</v>
@@ -5110,7 +5104,7 @@
         <v>281</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K43" s="9" t="s">
         <v>187</v>
@@ -5142,7 +5136,7 @@
         <v>15</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>382</v>
@@ -5166,7 +5160,7 @@
         <v>281</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K44" s="9" t="s">
         <v>189</v>
@@ -5198,7 +5192,7 @@
         <v>15</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>382</v>
@@ -5222,7 +5216,7 @@
         <v>292</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>191</v>
@@ -5254,7 +5248,7 @@
         <v>15</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>385</v>
@@ -5278,7 +5272,7 @@
         <v>297</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K46" s="9" t="s">
         <v>193</v>
@@ -5322,7 +5316,7 @@
         <v>15</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>386</v>
@@ -5346,7 +5340,7 @@
         <v>292</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>199</v>
@@ -5393,7 +5387,7 @@
         <v>15</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>388</v>
@@ -5417,7 +5411,7 @@
         <v>281</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K48" s="9" t="s">
         <v>206</v>
@@ -5446,7 +5440,7 @@
         <v>15</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>388</v>
@@ -5470,7 +5464,7 @@
         <v>281</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>207</v>
@@ -5508,7 +5502,7 @@
         <v>15</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>392</v>
@@ -5532,7 +5526,7 @@
         <v>281</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K50" s="9" t="s">
         <v>211</v>
@@ -5579,7 +5573,7 @@
         <v>15</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>393</v>
@@ -5603,7 +5597,7 @@
         <v>286</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>218</v>
@@ -5635,7 +5629,7 @@
         <v>15</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>396</v>
@@ -5659,7 +5653,7 @@
         <v>292</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K52" s="9" t="s">
         <v>220</v>
@@ -5706,7 +5700,7 @@
         <v>15</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>399</v>
@@ -5715,10 +5709,10 @@
         <v>1</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>401</v>
+        <v>289</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>290</v>
@@ -5730,7 +5724,7 @@
         <v>292</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>227</v>
@@ -5777,19 +5771,19 @@
         <v>15</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D54" s="8">
         <v>2</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>285</v>
@@ -5801,7 +5795,7 @@
         <v>331</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K54" s="9" t="s">
         <v>234</v>
@@ -5839,16 +5833,16 @@
         <v>15</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D55" s="8">
         <v>3</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>279</v>
@@ -5863,7 +5857,7 @@
         <v>281</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K55" s="9" t="s">
         <v>238</v>
@@ -5892,22 +5886,22 @@
         <v>15</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D56" s="8">
         <v>1</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>403</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>405</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>331</v>
@@ -5916,7 +5910,7 @@
         <v>331</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K56" s="9" t="s">
         <v>239</v>
@@ -5948,16 +5942,16 @@
         <v>15</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D57" s="8">
         <v>1</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>370</v>
@@ -5972,7 +5966,7 @@
         <v>292</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K57" s="9" t="s">
         <v>241</v>
@@ -6001,10 +5995,10 @@
         <v>15</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D58" s="7">
         <v>1</v>
@@ -6025,7 +6019,7 @@
         <v>281</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K58" s="9" t="s">
         <v>242</v>
@@ -6066,10 +6060,10 @@
         <v>15</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D59" s="7">
         <v>2</v>
@@ -6090,7 +6084,7 @@
         <v>306</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K59" s="9" t="s">
         <v>247</v>
@@ -6131,10 +6125,10 @@
         <v>15</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D60" s="7">
         <v>3</v>
@@ -6155,7 +6149,7 @@
         <v>286</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K60" s="9" t="s">
         <v>251</v>
@@ -6196,16 +6190,16 @@
         <v>15</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D61" s="14">
         <v>1</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F61" s="13" t="s">
         <v>289</v>
@@ -6220,7 +6214,7 @@
         <v>286</v>
       </c>
       <c r="J61" s="13" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K61" s="9" t="s">
         <v>256</v>
@@ -6264,10 +6258,10 @@
         <v>262</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D62" s="17"/>
       <c r="E62" s="16"/>
@@ -6276,7 +6270,7 @@
       <c r="H62" s="16"/>
       <c r="I62" s="16"/>
       <c r="J62" s="20" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K62" s="15"/>
       <c r="L62" s="15"/>
@@ -6296,10 +6290,10 @@
         <v>262</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D63" s="17"/>
       <c r="E63" s="16"/>
@@ -6308,7 +6302,7 @@
       <c r="H63" s="16"/>
       <c r="I63" s="16"/>
       <c r="J63" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K63" s="15"/>
       <c r="L63" s="15"/>
@@ -6332,10 +6326,10 @@
         <v>262</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D64" s="17"/>
       <c r="E64" s="16"/>
@@ -6344,7 +6338,7 @@
       <c r="H64" s="16"/>
       <c r="I64" s="16"/>
       <c r="J64" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K64" s="15"/>
       <c r="L64" s="15"/>
@@ -6364,10 +6358,10 @@
         <v>262</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D65" s="17"/>
       <c r="E65" s="16"/>
@@ -6376,7 +6370,7 @@
       <c r="H65" s="16"/>
       <c r="I65" s="16"/>
       <c r="J65" s="12" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K65" s="15"/>
       <c r="L65" s="15"/>
@@ -6396,10 +6390,10 @@
         <v>262</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D66" s="17"/>
       <c r="E66" s="16"/>
@@ -6408,7 +6402,7 @@
       <c r="H66" s="16"/>
       <c r="I66" s="16"/>
       <c r="J66" s="23" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K66" s="15"/>
       <c r="L66" s="15"/>
@@ -6428,13 +6422,13 @@
         <v>262</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
